--- a/即出荷2_肉付け版.xlsx
+++ b/即出荷2_肉付け版.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,25 +29,11 @@
     <font>
       <name val="HGP創英角ｺﾞｼｯｸUB"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="HGP創英角ｺﾞｼｯｸUB"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="HGP創英角ｺﾞｼｯｸUB"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="HGP創英角ｺﾞｼｯｸUB"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="HGP創英角ｺﾞｼｯｸUB"/>
@@ -67,7 +53,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -78,18 +64,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00BFBFBF"/>
         <bgColor rgb="00BFBFBF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,72 +119,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -578,211 +525,413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="B1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10.33" customWidth="1" min="1" max="1"/>
+    <col width="10.16" customWidth="1" min="2" max="2"/>
+    <col width="8.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="8.5" customWidth="1" min="6" max="6"/>
+    <col width="8.5" customWidth="1" min="7" max="7"/>
+    <col width="8.5" customWidth="1" min="8" max="8"/>
+    <col width="10.33" customWidth="1" min="9" max="9"/>
+    <col width="6.33" customWidth="1" min="10" max="10"/>
+    <col width="8.33" customWidth="1" min="11" max="11"/>
+    <col width="8.5" customWidth="1" min="12" max="12"/>
+    <col width="8.5" customWidth="1" min="13" max="13"/>
+    <col width="9.33" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>【即出荷】 事前準備チェックリスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※この準備が完了したら【即出荷】(2) シートへ。棚付けをする場合は【棚付け】シートへ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>確認項目</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>確認ポイント</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>標準作業手順書</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>文書番号: 02-中RC-AP-02-0019</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>作業項目: 【即出荷】事前準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>この準備が完了したら【即出荷】(2) シートへ。
+・棚付けをする場合 → 作業項目【棚付け】→ 手順【1】へ
+・即出荷をする場合 → 準備完了後、【即出荷】(2) 手順【1】へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>手順No.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>時間(秒)</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>急所</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>タブレットD（通過検品_即出荷）の電源ON</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>ロック解除後、WMSアプリが起動しているか確認</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>スキャナ接続も確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>タブレットD（通過検品_即出荷）の電源をONにし、スキャナの動作を確認する</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1">
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>WMSアプリが起動しているか確認する。
+スキャナでバーコードをテストスキャンし、正常に読み取れるか確認する。</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>スキャナ（タブレットD接続）の動作確認</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>バーコードを読み取れるかテストスキャン</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>梱包資材の在庫を確認し、作業台に準備する</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="N19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>確認する資材:
+・出荷箱（各サイズ: No.6・No.8・S18 等）
+・クラフトテープ / OPPテープ
+・緩衝材（エアーキャップ等）
+不足している場合はリーダーへ連絡すること。</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>「納品書在中」スタンプとスタンプ台の準備</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>インク残量確認</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>「納品書在中」スタンプとスタンプ台を準備する</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="N31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>スタンプ台のインク残量を確認する。
+薄い場合は補充またはリーダーへ連絡すること。</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>梱包資材の在庫確認</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>出荷箱（各サイズ）・クラフトテープ・OPPテープ・緩衝材</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>不足時はリーダーへ連絡</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>工程内不良カードの場所確認</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>所定の棚にあるか確認</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>【oLPN分割】シート参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>作業台（HP側 or 転送側）の決定</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>担当割振りに従い使用エリアを確認</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>転送側はドーリーも準備</t>
-        </is>
-      </c>
-    </row>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>工程内不良カードの場所を確認し、作業エリアを決定する</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr"/>
+      <c r="N43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>工程内不良カードが所定の棚にあるか確認する。
+（詳細: 【oLPN分割】シート参照）
+作業エリアの決定:
+・HP側の場合    → ドーリー不要
+・転送側の場合  → ドーリーを事前に作業台横に準備する</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1"/>
+    <row r="52" ht="22" customHeight="1">
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="63">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K22:M24"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="K40:M42"/>
+    <mergeCell ref="K31:M33"/>
+    <mergeCell ref="N19:T30"/>
+    <mergeCell ref="I19:I30"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="N6:T6"/>
+    <mergeCell ref="C7:H12"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="N31:T42"/>
+    <mergeCell ref="K43:M45"/>
+    <mergeCell ref="K52:M54"/>
+    <mergeCell ref="C19:H24"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="I31:I42"/>
+    <mergeCell ref="K46:M48"/>
+    <mergeCell ref="J52:J54"/>
+    <mergeCell ref="C13:H18"/>
+    <mergeCell ref="N7:T18"/>
+    <mergeCell ref="C37:H42"/>
+    <mergeCell ref="K13:M15"/>
+    <mergeCell ref="B37:B42"/>
+    <mergeCell ref="I7:I18"/>
+    <mergeCell ref="C49:H54"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="K10:M12"/>
+    <mergeCell ref="K28:M30"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K37:M39"/>
+    <mergeCell ref="K7:M9"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="K49:M51"/>
+    <mergeCell ref="K25:M27"/>
+    <mergeCell ref="K34:M36"/>
+    <mergeCell ref="N43:T54"/>
+    <mergeCell ref="K16:M18"/>
+    <mergeCell ref="C25:H30"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="K19:M21"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="I43:I54"/>
+    <mergeCell ref="B3:M5"/>
+    <mergeCell ref="C31:H36"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C43:H48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -794,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T162"/>
+  <dimension ref="B1:T150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.33" customWidth="1" min="1" max="1"/>
@@ -814,26 +963,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>標準作業手順書</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>文書番号: 02-中RC-AP-02-0019</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>作業項目: 【即出荷】</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>【場合分け】
 ・棚付けをする場合
@@ -846,385 +995,315 @@
     <row r="4" ht="20" customHeight="1"/>
     <row r="5" ht="20" customHeight="1"/>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>手順No.</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>時間(秒)</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>急所</t>
         </is>
       </c>
-      <c r="K6" s="15" t="n"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>写真</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>ラベルを確認する</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>オリコンを作業台に移動し、開閉して商品を取り出す</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>オリコン開閉時、空中作業・片手作業は禁止</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1"/>
     <row r="9" ht="22" customHeight="1"/>
     <row r="10" ht="22" customHeight="1">
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>指を挟む危険があるため（過去に挟み事故あり）</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1"/>
     <row r="12" ht="22" customHeight="1"/>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>部材の場合、1つのオリコンに複数ラベルが貼ってある。
-すべてのラベルを確認してから作業開始すること。
-・棚付けをする場合　→ 【棚付け】手順【1】へ
-・即出荷の場合　　　→ 手順【2】へ</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>HP側：オリコンを作業台に引き込む
+転送側：ドーリーを持ってきて作業台にオリコンを置く
+開閉手順は付表①シート参照。必ず両手・置いた状態で開閉する。
+封が閉まっている箱・袋は開梱せずそのまま使用する。
+・棚付けをする場合 → 作業項目【棚付け】→ 手順【1】へ
+・即出荷の場合　　 → そのまま手順【2】へ</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>ラベル枚数・発送先・品番・数量の確認漏れ厳禁</t>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>封が閉まっている箱・シーラ袋はそのまま使用（開梱して取り出さない）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1"/>
     <row r="15" ht="22" customHeight="1"/>
     <row r="16" ht="22" customHeight="1">
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>ラベル見落としは誤出荷の直接原因になるため</t>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>開梱時の商品落下→数量違い発生のため</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1"/>
     <row r="18" ht="22" customHeight="1"/>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>オリコンを作業台に移動し、開閉して商品を取り出す</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>商品を1点ずつ梱包台に置く</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>オリコン開閉時、空中作業・片手作業は禁止</t>
-        </is>
-      </c>
-      <c r="N19" s="22" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>西側：倒れやすい長物品は商品を押さえて取る</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1"/>
     <row r="21" ht="22" customHeight="1"/>
     <row r="22" ht="22" customHeight="1">
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>指を挟む危険があるため（過去に挟み事故あり）</t>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>過去に長尺品がバランスを崩し目に入る事故が発生したため</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1"/>
     <row r="24" ht="22" customHeight="1"/>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>HP側：オリコンを作業台に引き込む
-転送側：ドーリーを持ってきて作業台にオリコンを置く
-開閉手順は付表①シート参照。必ず両手・置いた状態で開閉する。
-封が閉まっている箱・袋は開梱せずそのまま使用する。</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>西側・転送作業場での作業時、商品を1点ずつ梱包台に置く。
+西側での長物品は商品を押さえながら取ること。
+作業台の上は必ず1オーダー分のみ
+（同じお客様名でも送り先が違う場合は混在禁止）</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>封が閉まっている箱・シーラ袋はそのまま使用（開梱して取り出さない）</t>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>作業台は1オーダー分のみ。送り先の異なる商品の混在禁止</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1"/>
     <row r="27" ht="22" customHeight="1"/>
     <row r="28" ht="22" customHeight="1">
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>開梱時の商品落下→数量違い発生のため</t>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>他のお客様の商品が混入するのを防ぐため</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1"/>
     <row r="30" ht="22" customHeight="1"/>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>商品を1点ずつ梱包台に置く</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr"/>
-      <c r="J31" s="20" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>商品サイズに合った出荷箱を選定し、底面にクラフトテープを貼る</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>西側：倒れやすい長物品は商品を押さえて取る</t>
-        </is>
-      </c>
-      <c r="N31" s="22" t="inlineStr"/>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="N31" s="13" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1"/>
     <row r="33" ht="22" customHeight="1"/>
     <row r="34" ht="22" customHeight="1">
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>過去に長尺品がバランスを崩し目に入る事故が発生したため</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1"/>
     <row r="36" ht="22" customHeight="1"/>
     <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>西側・転送作業場での作業時、商品を1点ずつ梱包台に置く。
-西側での長物品は商品を押さえながら取ること。
-作業台の上は必ず1オーダー分のみ（同じお客様名でも送り先が違う場合は混在禁止）。</t>
-        </is>
-      </c>
-      <c r="J37" s="20" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>目安: オリコン ≒ No.8箱（同サイズ）
+①十字張り → 片手で持てない重量品
+②H張り   → No.6以上の大箱（1辺の半分以上の長さを使用）</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>作業台は1オーダー分のみ。送り先の異なる商品の混在禁止</t>
+      <c r="K37" s="12" t="inlineStr">
+        <is>
+          <t>商品重量・サイズに応じたテープの貼り方を選定</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1"/>
     <row r="39" ht="22" customHeight="1"/>
     <row r="40" ht="22" customHeight="1">
-      <c r="J40" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K40" s="21" t="inlineStr">
-        <is>
-          <t>他のお客様の商品が混入するのを防ぐため</t>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>貼り方不足による底抜け→商品破損につながるため</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1"/>
     <row r="42" ht="22" customHeight="1"/>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>商品サイズに合った出荷箱を選定し、底面にクラフトテープを貼る</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr"/>
-      <c r="J43" s="20" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>底面に緩衝材を敷き、カウントしながら商品を箱に入れる</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K43" s="21" t="inlineStr"/>
-      <c r="N43" s="22" t="inlineStr"/>
+      <c r="K43" s="12" t="inlineStr"/>
+      <c r="N43" s="13" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1"/>
     <row r="45" ht="22" customHeight="1"/>
     <row r="46" ht="22" customHeight="1">
-      <c r="J46" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K46" s="21" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr"/>
     </row>
     <row r="47" ht="22" customHeight="1"/>
     <row r="48" ht="22" customHeight="1"/>
     <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>目安: オリコン ≒ No.8箱（同サイズ）
-①十字張り → 片手で持てない重量品
-②H張り   → No.6以上の大箱（1辺の半分以上の長さを使用）</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>Q:</t>
-        </is>
-      </c>
-      <c r="K49" s="21" t="inlineStr">
-        <is>
-          <t>商品重量・サイズに応じたテープの貼り方を選定</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1"/>
-    <row r="51" ht="22" customHeight="1"/>
-    <row r="52" ht="22" customHeight="1">
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>貼り方不足による底抜け→商品破損につながるため</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1"/>
-    <row r="54" ht="22" customHeight="1"/>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>底面に緩衝材を敷き、カウントしながら商品を箱に入れる</t>
-        </is>
-      </c>
-      <c r="I55" s="19" t="inlineStr"/>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>S:</t>
-        </is>
-      </c>
-      <c r="K55" s="21" t="inlineStr"/>
-      <c r="N55" s="22" t="inlineStr"/>
-    </row>
-    <row r="56" ht="22" customHeight="1"/>
-    <row r="57" ht="22" customHeight="1"/>
-    <row r="58" ht="22" customHeight="1">
-      <c r="J58" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K58" s="21" t="inlineStr"/>
-    </row>
-    <row r="59" ht="22" customHeight="1"/>
-    <row r="60" ht="22" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="23" t="inlineStr">
-        <is>
-          <t>補足:</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>特性フラグを確認すること。
 ・パック品：2ピース以上のまとまり → バラさずカウント
@@ -1233,72 +1312,72 @@
 メーカー箱の場合: 箱側面のメーカー入数を必ず確認し、赤丸をつける。</t>
         </is>
       </c>
-      <c r="J61" s="20" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K61" s="21" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>底面・側面が隠れるよう緩衝材を敷く。入数情報を確認し赤丸をつける</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1"/>
-    <row r="63" ht="22" customHeight="1"/>
-    <row r="64" ht="22" customHeight="1">
-      <c r="J64" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K64" s="21" t="inlineStr">
-        <is>
-          <t>緩衝材不足→破損 / 赤丸なし→数量確認抜け漏れ防止のため</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1"/>
-    <row r="66" ht="22" customHeight="1"/>
-    <row r="67" ht="22" customHeight="1">
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
+    <row r="50" ht="22" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1"/>
+    <row r="52" ht="22" customHeight="1">
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>緩衝材不足→破損 / 赤丸なし→数量確認漏れ防止のため</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>カウント数がピックラベルの数量と一致しているか確認し、赤丸をつける</t>
         </is>
       </c>
-      <c r="I67" s="19" t="inlineStr"/>
-      <c r="J67" s="20" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K67" s="21" t="inlineStr"/>
-      <c r="N67" s="22" t="inlineStr"/>
-    </row>
-    <row r="68" ht="22" customHeight="1"/>
-    <row r="69" ht="22" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="J70" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K70" s="21" t="inlineStr"/>
-    </row>
-    <row r="71" ht="22" customHeight="1"/>
-    <row r="72" ht="22" customHeight="1"/>
-    <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="23" t="inlineStr">
+      <c r="K55" s="12" t="inlineStr"/>
+      <c r="N55" s="13" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1">
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1"/>
+    <row r="60" ht="22" customHeight="1"/>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C73" s="24" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>一致しない場合 → 工程内不良カードを記入し、管理社員へ渡す
 　（→ 作業項目【oLPN分割】→ 工程内不良カード記載へ）
@@ -1306,351 +1385,362 @@
 ①日付 ②不良内容 ③④品番・ラベル情報 ⑤自身の氏名</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K73" s="21" t="inlineStr">
+      <c r="K61" s="12" t="inlineStr">
         <is>
           <t>部材品は並べてカウント。点数と番号を両方チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1">
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>1個単位の数量違いが最多ミスのため、並べることで視認精度を上げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1"/>
+    <row r="66" ht="22" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>ラベルを確認する</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr"/>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr"/>
+      <c r="N67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68" ht="22" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71" ht="22" customHeight="1"/>
+    <row r="72" ht="22" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1">
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>梱包が完了し赤丸をつけた後、ラベルの内容を確認する。
+・発送先・品番・数量がピックラベルと一致しているか
+・部材の場合、1つのオリコンに複数ラベルが貼ってあるので確認漏れに注意</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>ラベルの発送先・品番・数量の確認漏れ厳禁</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1"/>
     <row r="75" ht="22" customHeight="1"/>
     <row r="76" ht="22" customHeight="1">
-      <c r="J76" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K76" s="21" t="inlineStr">
-        <is>
-          <t>1個単位の数量違いが最多ミスのため、並べることで視認精度を上げる</t>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>梱包後のラベル照合が誤出荷を防ぐ最後の砦となるため</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1"/>
     <row r="78" ht="22" customHeight="1"/>
     <row r="79" ht="22" customHeight="1">
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>タブレットD（通過検品_即出荷）のスキャナで
-G#（OLPN）ラベルをスキャンする</t>
-        </is>
-      </c>
-      <c r="I79" s="19" t="inlineStr"/>
-      <c r="J79" s="20" t="inlineStr">
+G#（OLPN）ラベルをスキャンし、バッチを確認する</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K79" s="21" t="inlineStr"/>
-      <c r="N79" s="22" t="inlineStr"/>
+      <c r="K79" s="12" t="inlineStr"/>
+      <c r="N79" s="13" t="inlineStr"/>
     </row>
     <row r="80" ht="22" customHeight="1"/>
     <row r="81" ht="22" customHeight="1"/>
     <row r="82" ht="22" customHeight="1">
-      <c r="J82" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K82" s="21" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="22" customHeight="1"/>
     <row r="84" ht="22" customHeight="1"/>
     <row r="85" ht="22" customHeight="1">
-      <c r="B85" s="23" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C85" s="24" t="inlineStr">
-        <is>
-          <t>20kg以上の商品・S18箱にしか入らない商品は
-配送方法をQ/T（キャリー/ヤマト）→ S（佐川）へ切り替えること。</t>
-        </is>
-      </c>
-      <c r="J85" s="20" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>スキャン後、以下が発行される:
+①納品書   → 残1梱包のみ出力（複数枚出ることあり）
+②送り状   → シューター番号を納品書と照合
+③ランクラベル → ランクオーダーのみ出力
+20kg以上・S18箱のみの商品は配送方法を Q/T → S（佐川）へ切り替えること。</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K85" s="21" t="inlineStr"/>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>納品書と送り状のシューター番号が一致しているか確認</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1"/>
     <row r="87" ht="22" customHeight="1"/>
     <row r="88" ht="22" customHeight="1">
-      <c r="J88" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K88" s="21" t="inlineStr"/>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>印刷機トラブル等で直前の別注文と混在しないため（誤配送防止）</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1"/>
     <row r="90" ht="22" customHeight="1"/>
     <row r="91" ht="22" customHeight="1">
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>発行された納品書・送り状・ランクラベルを受け取り確認する</t>
-        </is>
-      </c>
-      <c r="I91" s="19" t="inlineStr"/>
-      <c r="J91" s="20" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>送り状を箱の長手面・右上に貼り付ける</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr"/>
+      <c r="J91" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K91" s="21" t="inlineStr"/>
-      <c r="N91" s="22" t="inlineStr"/>
+      <c r="K91" s="12" t="inlineStr"/>
+      <c r="N91" s="13" t="inlineStr"/>
     </row>
     <row r="92" ht="22" customHeight="1"/>
     <row r="93" ht="22" customHeight="1"/>
     <row r="94" ht="22" customHeight="1">
-      <c r="J94" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K94" s="21" t="inlineStr"/>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95" ht="22" customHeight="1"/>
     <row r="96" ht="22" customHeight="1"/>
     <row r="97" ht="22" customHeight="1">
-      <c r="B97" s="23" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C97" s="24" t="inlineStr">
-        <is>
-          <t>①納品書  → 残1梱包のみ出力（複数枚出ることあり）
-②送り状  → シューター番号を納品書と照合
-③ランクラベル → ランクオーダーのみ出力</t>
-        </is>
-      </c>
-      <c r="J97" s="20" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>箱の長い面（長手面）の右上に貼る。
+広告印刷がある場合は、なるべく見える位置を選ぶ。</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K97" s="21" t="inlineStr">
-        <is>
-          <t>納品書と送り状のシューター番号が一致しているか確認</t>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>送り状の貼り忘れ厳禁</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1"/>
     <row r="99" ht="22" customHeight="1"/>
     <row r="100" ht="22" customHeight="1">
-      <c r="J100" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K100" s="21" t="inlineStr">
-        <is>
-          <t>印刷機トラブル等で直前の別注文のものと混在しないため（誤配送防止）</t>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>送り状がないと荷合せ不能 / お客様が届いた商品の内容不明になるため</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1"/>
     <row r="102" ht="22" customHeight="1"/>
     <row r="103" ht="22" customHeight="1">
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>送り状を箱の長手面・右上に貼り付ける</t>
-        </is>
-      </c>
-      <c r="I103" s="19" t="inlineStr"/>
-      <c r="J103" s="20" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>上部まで緩衝材を詰めて封緘（クラフトテープ）を行う</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr"/>
+      <c r="J103" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K103" s="21" t="inlineStr"/>
-      <c r="N103" s="22" t="inlineStr"/>
+      <c r="K103" s="12" t="inlineStr"/>
+      <c r="N103" s="13" t="inlineStr"/>
     </row>
     <row r="104" ht="22" customHeight="1"/>
     <row r="105" ht="22" customHeight="1"/>
     <row r="106" ht="22" customHeight="1">
-      <c r="J106" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K106" s="21" t="inlineStr"/>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr"/>
     </row>
     <row r="107" ht="22" customHeight="1"/>
     <row r="108" ht="22" customHeight="1"/>
     <row r="109" ht="22" customHeight="1">
-      <c r="B109" s="23" t="inlineStr">
+      <c r="B109" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C109" s="24" t="inlineStr">
-        <is>
-          <t>箱の長い面（長手面）の右上に貼る。
-広告印刷がある場合は、なるべく見える位置を選ぶ。</t>
-        </is>
-      </c>
-      <c r="J109" s="20" t="inlineStr">
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>袋の場合：開封口を1回折り込みOPPテープで止め、その後箱に入れる
+箱の場合：天面をクラフトテープで封緘
+封緘後に必ず箱を振って商品が動かないか確認する。</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K109" s="21" t="inlineStr">
-        <is>
-          <t>送り状の貼り忘れ厳禁</t>
+      <c r="K109" s="12" t="inlineStr">
+        <is>
+          <t>封緘後に箱を振って、中で商品が動かないか確認する。破損箱は交換</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1"/>
     <row r="111" ht="22" customHeight="1"/>
     <row r="112" ht="22" customHeight="1">
-      <c r="J112" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K112" s="21" t="inlineStr">
-        <is>
-          <t>送り状がないと荷合せ不能 / お客様が届いた商品の内容不明になるため</t>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr">
+        <is>
+          <t>輸送中の振動・衝撃による商品・箱の破損防止のため</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1"/>
     <row r="114" ht="22" customHeight="1"/>
     <row r="115" ht="22" customHeight="1">
-      <c r="B115" s="17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
-        <is>
-          <t>上部まで緩衝材を詰めて封緘（クラフトテープ）を行う</t>
-        </is>
-      </c>
-      <c r="I115" s="19" t="inlineStr"/>
-      <c r="J115" s="20" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>「納品書在中」印を捺印し、ランクラベルを商品ラベルの左隣に貼る</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="inlineStr"/>
+      <c r="J115" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K115" s="21" t="inlineStr"/>
-      <c r="N115" s="22" t="inlineStr"/>
+      <c r="K115" s="12" t="inlineStr"/>
+      <c r="N115" s="13" t="inlineStr"/>
     </row>
     <row r="116" ht="22" customHeight="1"/>
     <row r="117" ht="22" customHeight="1"/>
     <row r="118" ht="22" customHeight="1">
-      <c r="J118" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K118" s="21" t="inlineStr"/>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="inlineStr"/>
     </row>
     <row r="119" ht="22" customHeight="1"/>
     <row r="120" ht="22" customHeight="1"/>
     <row r="121" ht="22" customHeight="1">
-      <c r="B121" s="23" t="inlineStr">
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>袋の場合：開封口を1回折り込みOPPテープで止め、その後箱に入れる
-箱の場合：天面をクラフトテープで封緘
-封緘後に必ず箱を振って商品が動かないか確認する。</t>
-        </is>
-      </c>
-      <c r="J121" s="20" t="inlineStr">
-        <is>
-          <t>Q:</t>
-        </is>
-      </c>
-      <c r="K121" s="21" t="inlineStr">
-        <is>
-          <t>封緘後に箱を振って、中で商品が動かないか確認する。破損箱は交換</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1"/>
-    <row r="124" ht="22" customHeight="1">
-      <c r="J124" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K124" s="21" t="inlineStr">
-        <is>
-          <t>輸送中の振動・衝撃による商品・箱の破損防止のため</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="22" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1">
-      <c r="B127" s="17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>「納品書在中」印を捺印し、ランクラベルを商品ラベルの左隣に貼る</t>
-        </is>
-      </c>
-      <c r="I127" s="19" t="inlineStr"/>
-      <c r="J127" s="20" t="inlineStr">
-        <is>
-          <t>S:</t>
-        </is>
-      </c>
-      <c r="K127" s="21" t="inlineStr"/>
-      <c r="N127" s="22" t="inlineStr"/>
-    </row>
-    <row r="128" ht="22" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1"/>
-    <row r="130" ht="22" customHeight="1">
-      <c r="J130" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K130" s="21" t="inlineStr"/>
-    </row>
-    <row r="131" ht="22" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1">
-      <c r="B133" s="23" t="inlineStr">
-        <is>
-          <t>補足:</t>
-        </is>
-      </c>
-      <c r="C133" s="24" t="inlineStr">
+      <c r="C121" s="15" t="inlineStr">
         <is>
           <t>「納品書在中」スタンプ：送り状から見て左上、広告と被らない位置に捺印
 ランクラベル：商品ラベルの左隣に貼付
@@ -1659,153 +1749,153 @@
 ・上記以外の場合 → 手順13へ</t>
         </is>
       </c>
-      <c r="J133" s="20" t="inlineStr">
+      <c r="J121" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K133" s="21" t="inlineStr"/>
+      <c r="K121" s="12" t="inlineStr"/>
+    </row>
+    <row r="122" ht="22" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1"/>
+    <row r="124" ht="22" customHeight="1">
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="22" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1">
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>【特定伝・指定伝のみ】封緘を実施し、所定置場へ搬送する</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr"/>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>S:</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="inlineStr"/>
+      <c r="N127" s="13" t="inlineStr"/>
+    </row>
+    <row r="128" ht="22" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1">
+      <c r="J130" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="inlineStr"/>
+    </row>
+    <row r="131" ht="22" customHeight="1"/>
+    <row r="132" ht="22" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1">
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>補足:</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>手順10と同じ封緘作業を実施する。
+搬送先: 特定指定伝N品置場</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="inlineStr">
+        <is>
+          <t>Q:</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="inlineStr"/>
     </row>
     <row r="134" ht="22" customHeight="1"/>
     <row r="135" ht="22" customHeight="1"/>
     <row r="136" ht="22" customHeight="1">
-      <c r="J136" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K136" s="21" t="inlineStr"/>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="22" customHeight="1"/>
     <row r="138" ht="22" customHeight="1"/>
     <row r="139" ht="22" customHeight="1">
-      <c r="B139" s="17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>【特定伝・指定伝のみ】封緘を実施し、所定置場へ搬送する</t>
-        </is>
-      </c>
-      <c r="I139" s="19" t="inlineStr"/>
-      <c r="J139" s="20" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>出荷箱を所定の置場へ搬送する</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="inlineStr"/>
+      <c r="J139" s="11" t="inlineStr">
         <is>
           <t>S:</t>
         </is>
       </c>
-      <c r="K139" s="21" t="inlineStr"/>
-      <c r="N139" s="22" t="inlineStr"/>
+      <c r="K139" s="12" t="inlineStr"/>
+      <c r="N139" s="13" t="inlineStr"/>
     </row>
     <row r="140" ht="22" customHeight="1"/>
     <row r="141" ht="22" customHeight="1"/>
     <row r="142" ht="22" customHeight="1">
-      <c r="J142" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K142" s="21" t="inlineStr"/>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr"/>
     </row>
     <row r="143" ht="22" customHeight="1"/>
     <row r="144" ht="22" customHeight="1"/>
     <row r="145" ht="22" customHeight="1">
-      <c r="B145" s="23" t="inlineStr">
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>補足:</t>
         </is>
       </c>
-      <c r="C145" s="24" t="inlineStr">
-        <is>
-          <t>手順10と同じ封緘作業を実施する。
-搬送先: 特定指定伝N品置場</t>
-        </is>
-      </c>
-      <c r="J145" s="20" t="inlineStr">
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>前当(前日注文当日出荷)の場合 → 3F 入出荷エリアへ
+当1・当2・当3の場合 → 4F 指定伝梱包台へ</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
         <is>
           <t>Q:</t>
         </is>
       </c>
-      <c r="K145" s="21" t="inlineStr"/>
+      <c r="K145" s="12" t="inlineStr"/>
     </row>
     <row r="146" ht="22" customHeight="1"/>
     <row r="147" ht="22" customHeight="1"/>
     <row r="148" ht="22" customHeight="1">
-      <c r="J148" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K148" s="21" t="inlineStr"/>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>理由:</t>
+        </is>
+      </c>
+      <c r="K148" s="12" t="inlineStr"/>
     </row>
     <row r="149" ht="22" customHeight="1"/>
     <row r="150" ht="22" customHeight="1"/>
-    <row r="151" ht="22" customHeight="1">
-      <c r="B151" s="17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>出荷箱を所定の置場へ搬送する</t>
-        </is>
-      </c>
-      <c r="I151" s="19" t="inlineStr"/>
-      <c r="J151" s="20" t="inlineStr">
-        <is>
-          <t>S:</t>
-        </is>
-      </c>
-      <c r="K151" s="21" t="inlineStr"/>
-      <c r="N151" s="22" t="inlineStr"/>
-    </row>
-    <row r="152" ht="22" customHeight="1"/>
-    <row r="153" ht="22" customHeight="1"/>
-    <row r="154" ht="22" customHeight="1">
-      <c r="J154" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K154" s="21" t="inlineStr"/>
-    </row>
-    <row r="155" ht="22" customHeight="1"/>
-    <row r="156" ht="22" customHeight="1"/>
-    <row r="157" ht="22" customHeight="1">
-      <c r="B157" s="23" t="inlineStr">
-        <is>
-          <t>補足:</t>
-        </is>
-      </c>
-      <c r="C157" s="24" t="inlineStr">
-        <is>
-          <t>前当(前日注文当日出荷)の場合 → 3F 入出荷エリアへ
-当1・当2・当3の場合 → 4F 指定伝梱包台へ</t>
-        </is>
-      </c>
-      <c r="J157" s="20" t="inlineStr">
-        <is>
-          <t>Q:</t>
-        </is>
-      </c>
-      <c r="K157" s="21" t="inlineStr"/>
-    </row>
-    <row r="158" ht="22" customHeight="1"/>
-    <row r="159" ht="22" customHeight="1"/>
-    <row r="160" ht="22" customHeight="1">
-      <c r="J160" s="20" t="inlineStr">
-        <is>
-          <t>理由:</t>
-        </is>
-      </c>
-      <c r="K160" s="21" t="inlineStr"/>
-    </row>
-    <row r="161" ht="22" customHeight="1"/>
-    <row r="162" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="189">
+  <mergeCells count="175">
     <mergeCell ref="I67:I78"/>
     <mergeCell ref="K94:M96"/>
     <mergeCell ref="J91:J93"/>
@@ -1820,12 +1910,8 @@
     <mergeCell ref="N139:T150"/>
     <mergeCell ref="K136:M138"/>
     <mergeCell ref="K70:M72"/>
-    <mergeCell ref="B157:B162"/>
-    <mergeCell ref="J160:J162"/>
-    <mergeCell ref="B151:B156"/>
     <mergeCell ref="J67:J69"/>
     <mergeCell ref="B67:B72"/>
-    <mergeCell ref="C157:H162"/>
     <mergeCell ref="J61:J63"/>
     <mergeCell ref="J97:J99"/>
     <mergeCell ref="C49:H54"/>
@@ -1835,7 +1921,6 @@
     <mergeCell ref="C103:H108"/>
     <mergeCell ref="C97:H102"/>
     <mergeCell ref="B103:B108"/>
-    <mergeCell ref="I151:I162"/>
     <mergeCell ref="K49:M51"/>
     <mergeCell ref="J136:J138"/>
     <mergeCell ref="K19:M21"/>
@@ -1847,9 +1932,7 @@
     <mergeCell ref="J55:J57"/>
     <mergeCell ref="C31:H36"/>
     <mergeCell ref="B55:B60"/>
-    <mergeCell ref="N151:T162"/>
     <mergeCell ref="K139:M141"/>
-    <mergeCell ref="K154:M156"/>
     <mergeCell ref="J70:J72"/>
     <mergeCell ref="B79:B84"/>
     <mergeCell ref="J79:J81"/>
@@ -1879,7 +1962,6 @@
     <mergeCell ref="B121:B126"/>
     <mergeCell ref="B73:B78"/>
     <mergeCell ref="K61:M63"/>
-    <mergeCell ref="K160:M162"/>
     <mergeCell ref="C73:H78"/>
     <mergeCell ref="I139:I150"/>
     <mergeCell ref="K97:M99"/>
@@ -1889,7 +1971,6 @@
     <mergeCell ref="J28:J30"/>
     <mergeCell ref="N43:T54"/>
     <mergeCell ref="J37:J39"/>
-    <mergeCell ref="J151:J153"/>
     <mergeCell ref="C25:H30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C85:H90"/>
@@ -1919,16 +2000,13 @@
     <mergeCell ref="J145:J147"/>
     <mergeCell ref="I31:I42"/>
     <mergeCell ref="J139:J141"/>
-    <mergeCell ref="J154:J156"/>
     <mergeCell ref="C13:H18"/>
     <mergeCell ref="C145:H150"/>
     <mergeCell ref="J76:J78"/>
     <mergeCell ref="N7:T18"/>
     <mergeCell ref="K148:M150"/>
     <mergeCell ref="C37:H42"/>
-    <mergeCell ref="K157:M159"/>
     <mergeCell ref="K13:M15"/>
-    <mergeCell ref="K151:M153"/>
     <mergeCell ref="N79:T90"/>
     <mergeCell ref="J73:J75"/>
     <mergeCell ref="J88:J90"/>
@@ -1946,7 +2024,6 @@
     <mergeCell ref="K112:M114"/>
     <mergeCell ref="C121:H126"/>
     <mergeCell ref="I91:I102"/>
-    <mergeCell ref="J157:J159"/>
     <mergeCell ref="I43:I54"/>
     <mergeCell ref="K118:M120"/>
     <mergeCell ref="K133:M135"/>
@@ -1973,7 +2050,6 @@
     <mergeCell ref="C19:H24"/>
     <mergeCell ref="K130:M132"/>
     <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C151:H156"/>
     <mergeCell ref="K145:M147"/>
     <mergeCell ref="K58:M60"/>
     <mergeCell ref="K67:M69"/>
